--- a/nonprofit_employee_forms/013_nonprofit_organization_feedback_questionnaire--nonprofit_employee_forms.xlsx
+++ b/nonprofit_employee_forms/013_nonprofit_organization_feedback_questionnaire--nonprofit_employee_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How often do you interact with our organization?</t>
+          <t>Nonprofit Organization Feedback Questionnaire Frequency Of Interaction</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How often do you contact our organization?</t>
+          <t>Nonprofit Organization Feedback Questionnaire Improve Services</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Which service(s) did you use?</t>
+          <t>Nonprofit Organization Feedback Questionnaire Improve Programs</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nonprofit_organization_feedback_questionnaire_improve_programs</t>
+          <t>nonprofit_organization_feedback_questionnaire_improve_programs_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Which service(s) did you use?</t>
+          <t>Nonprofit Organization Feedback Questionnaire Improve Programs 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nonprofit_organization_feedback_questionnaire_improve_services</t>
+          <t>nonprofit_organization_feedback_questionnaire_improve_services_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What could we improve about the services we provide?</t>
+          <t>Nonprofit Organization Feedback Questionnaire Improvement Suggestions</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nonprofit_organization_feedback_questionnaire_programs</t>
+          <t>nonprofit_organization_feedback_questionnaire_programs_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nonprofit_organization_feedback_questionnaire_services</t>
+          <t>nonprofit_organization_feedback_questionnaire_services_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>How often do you contact our organization?</t>
+          <t>Nonprofit Organization Feedback Questionnaire Contacted</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Which service do you interact with most frequently?</t>
+          <t>Nonprofit Organization Feedback Questionnaire Services Frequency</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nonprofit_organization_feedback_questionnaire_improve_programs</t>
+          <t>nonprofit_organization_feedback_questionnaire_improve_programs_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>What would improve your experience with our organization?</t>
+          <t>Nonprofit Organization Feedback Questionnaire Improve Programs 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nonprofit_organization_feedback_questionnaire_improve_services</t>
+          <t>nonprofit_organization_feedback_questionnaire_improve_services_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>What would improve your experience with our organization?</t>
+          <t>Nonprofit Organization Feedback Questionnaire Improve Services 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nonprofit_organization_feedback_questionnaire_improve_often</t>
+          <t>nonprofit_organization_feedback_questionnaire_improve_often_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>How would you like to improve the services we provide?</t>
+          <t>Nonprofit Organization Feedback Questionnaire Improve Often 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>How would you like to improve the services we provide?</t>
+          <t>Nonprofit Organization Feedback Questionnaire Improve Frequency</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>nonprofit_organization_feedback_questionnaire_improve_programs_choices</t>
+          <t>nonprofit_organization_feedback_questionnaire_improve_programs_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>nonprofit_organization_feedback_questionnaire_improve_programs_choices</t>
+          <t>nonprofit_organization_feedback_questionnaire_improve_programs_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>nonprofit_organization_feedback_questionnaire_improve_programs_choices</t>
+          <t>nonprofit_organization_feedback_questionnaire_improve_programs_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>nonprofit_organization_feedback_questionnaire_programs_choices</t>
+          <t>nonprofit_organization_feedback_questionnaire_programs_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1602,7 +1602,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>nonprofit_organization_feedback_questionnaire_programs_choices</t>
+          <t>nonprofit_organization_feedback_questionnaire_programs_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>nonprofit_organization_feedback_questionnaire_programs_choices</t>
+          <t>nonprofit_organization_feedback_questionnaire_programs_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1636,7 +1636,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>nonprofit_organization_feedback_questionnaire_services_choices</t>
+          <t>nonprofit_organization_feedback_questionnaire_services_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>nonprofit_organization_feedback_questionnaire_services_choices</t>
+          <t>nonprofit_organization_feedback_questionnaire_services_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1670,7 +1670,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>nonprofit_organization_feedback_questionnaire_services_choices</t>
+          <t>nonprofit_organization_feedback_questionnaire_services_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
